--- a/artfynd/A 14153-2025 artfynd.xlsx
+++ b/artfynd/A 14153-2025 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124302208</v>
+        <v>124287299</v>
       </c>
       <c r="B4" t="n">
-        <v>5492</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,43 +915,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101410</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hålsjön, Hålsjön, Srm</t>
+          <t>Svinsjön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634019</v>
+        <v>634167</v>
       </c>
       <c r="R4" t="n">
-        <v>6553615</v>
+        <v>6553564</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Cirka 0,5 - 1,5 m ovan mark på sydsidan av stammen på två tallar.</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gustaf Eibl</t>
+          <t>Anna Sahlberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gustaf Eibl</t>
+          <t>Anna Sahlberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124287299</v>
+        <v>124302208</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>5492</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,43 +1032,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>101410</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svinsjön, Srm</t>
+          <t>Hålsjön, Hålsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>634167</v>
+        <v>634019</v>
       </c>
       <c r="R5" t="n">
-        <v>6553564</v>
+        <v>6553615</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Cirka 0,5 - 1,5 m ovan mark på sydsidan av stammen på två tallar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,12 +1130,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna Sahlberg</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Sahlberg</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 14153-2025 artfynd.xlsx
+++ b/artfynd/A 14153-2025 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124287299</v>
+        <v>124302208</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>5492</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,43 +915,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>101410</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svinsjön, Srm</t>
+          <t>Hålsjön, Hålsjön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634167</v>
+        <v>634019</v>
       </c>
       <c r="R4" t="n">
-        <v>6553564</v>
+        <v>6553615</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Cirka 0,5 - 1,5 m ovan mark på sydsidan av stammen på två tallar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna Sahlberg</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Sahlberg</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124302208</v>
+        <v>124287299</v>
       </c>
       <c r="B5" t="n">
-        <v>5492</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,43 +1037,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101410</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hålsjön, Hålsjön, Srm</t>
+          <t>Svinsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>634019</v>
+        <v>634167</v>
       </c>
       <c r="R5" t="n">
-        <v>6553615</v>
+        <v>6553564</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Cirka 0,5 - 1,5 m ovan mark på sydsidan av stammen på två tallar.</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,12 +1130,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gustaf Eibl</t>
+          <t>Anna Sahlberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gustaf Eibl</t>
+          <t>Anna Sahlberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
